--- a/Data/EC/NIT-9004168798.xlsx
+++ b/Data/EC/NIT-9004168798.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB47270B-64E8-45EE-8C03-D047CF1153EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{071665A4-1890-4A08-988A-C8E57C99D874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4AE0A4FD-449F-4408-8BE7-19036B0FE734}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9330EFB1-68E6-415E-98BE-B084474A3FD2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -71,292 +71,292 @@
     <t>JORGE SANTIAGO PERTUZ MENDOZA</t>
   </si>
   <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
     <t>1608</t>
   </si>
   <si>
-    <t>1609</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>1612</t>
-  </si>
-  <si>
-    <t>1701</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
     <t>1047388602</t>
   </si>
   <si>
     <t>JOHN EDUARD ARREDONDO HUERTAS</t>
   </si>
   <si>
+    <t>2412</t>
+  </si>
+  <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>2406</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>2404</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>2312</t>
+  </si>
+  <si>
+    <t>2311</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>2309</t>
+  </si>
+  <si>
+    <t>2308</t>
+  </si>
+  <si>
+    <t>2307</t>
+  </si>
+  <si>
+    <t>2306</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
+    <t>2304</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>2302</t>
+  </si>
+  <si>
+    <t>2301</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>2207</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
     <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>2207</t>
-  </si>
-  <si>
-    <t>2208</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>2212</t>
-  </si>
-  <si>
-    <t>2301</t>
-  </si>
-  <si>
-    <t>2302</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>2304</t>
-  </si>
-  <si>
-    <t>2305</t>
-  </si>
-  <si>
-    <t>2306</t>
-  </si>
-  <si>
-    <t>2307</t>
-  </si>
-  <si>
-    <t>2308</t>
-  </si>
-  <si>
-    <t>2309</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>2311</t>
-  </si>
-  <si>
-    <t>2312</t>
-  </si>
-  <si>
-    <t>2401</t>
-  </si>
-  <si>
-    <t>2402</t>
-  </si>
-  <si>
-    <t>2403</t>
-  </si>
-  <si>
-    <t>2404</t>
-  </si>
-  <si>
-    <t>2405</t>
-  </si>
-  <si>
-    <t>2406</t>
-  </si>
-  <si>
-    <t>2407</t>
-  </si>
-  <si>
-    <t>2408</t>
-  </si>
-  <si>
-    <t>2409</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>2411</t>
-  </si>
-  <si>
-    <t>2412</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -455,9 +455,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -470,7 +468,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -670,23 +670,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -714,10 +714,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -755,22 +755,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24329855-BD82-F579-D151-68A4250E5B48}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7AAE46B-B0D8-F3E3-3401-E6DE59890EFB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -792,7 +792,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1121,23 +1121,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA0C850-E1D6-4B89-BCA5-E38BD439D810}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{914045E9-E9E4-421C-9742-6738AE32AEEA}">
   <dimension ref="B2:J115"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1150,7 +1150,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1161,7 +1161,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1172,7 +1172,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1183,8 +1183,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>108</v>
       </c>
@@ -1199,8 +1199,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1215,8 +1215,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>109</v>
       </c>
@@ -1231,8 +1231,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>110</v>
       </c>
@@ -1251,7 +1251,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1303,7 +1303,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1326,7 +1326,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1349,7 +1349,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1372,7 +1372,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1395,7 +1395,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1418,7 +1418,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1441,7 +1441,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>20</v>
       </c>
       <c r="F23" s="18">
-        <v>7861</v>
+        <v>20833</v>
       </c>
       <c r="G23" s="18">
         <v>781242</v>
@@ -1464,7 +1464,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>21</v>
       </c>
       <c r="F24" s="18">
-        <v>29480</v>
+        <v>31249</v>
       </c>
       <c r="G24" s="18">
         <v>781242</v>
@@ -1487,7 +1487,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>22</v>
       </c>
       <c r="F25" s="18">
-        <v>29480</v>
+        <v>31249</v>
       </c>
       <c r="G25" s="18">
         <v>781242</v>
@@ -1510,7 +1510,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>23</v>
       </c>
       <c r="F26" s="18">
-        <v>29480</v>
+        <v>31249</v>
       </c>
       <c r="G26" s="18">
         <v>781242</v>
@@ -1533,7 +1533,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>24</v>
       </c>
       <c r="F27" s="18">
-        <v>29480</v>
+        <v>31249</v>
       </c>
       <c r="G27" s="18">
         <v>781242</v>
@@ -1556,7 +1556,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>25</v>
       </c>
       <c r="F28" s="18">
-        <v>29480</v>
+        <v>31249</v>
       </c>
       <c r="G28" s="18">
         <v>781242</v>
@@ -1579,7 +1579,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>26</v>
       </c>
       <c r="F29" s="18">
-        <v>29480</v>
+        <v>31249</v>
       </c>
       <c r="G29" s="18">
         <v>781242</v>
@@ -1602,7 +1602,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>27</v>
       </c>
       <c r="F30" s="18">
-        <v>29480</v>
+        <v>31249</v>
       </c>
       <c r="G30" s="18">
         <v>781242</v>
@@ -1625,7 +1625,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>28</v>
       </c>
       <c r="F31" s="18">
-        <v>29480</v>
+        <v>31249</v>
       </c>
       <c r="G31" s="18">
         <v>781242</v>
@@ -1648,7 +1648,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>29</v>
       </c>
       <c r="F32" s="18">
-        <v>29480</v>
+        <v>31249</v>
       </c>
       <c r="G32" s="18">
         <v>781242</v>
@@ -1671,7 +1671,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>30</v>
       </c>
       <c r="F33" s="18">
-        <v>29480</v>
+        <v>31249</v>
       </c>
       <c r="G33" s="18">
         <v>781242</v>
@@ -1694,7 +1694,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1717,7 +1717,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1740,7 +1740,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1763,7 +1763,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1786,7 +1786,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1809,7 +1809,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1832,7 +1832,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1855,7 +1855,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1878,7 +1878,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1901,7 +1901,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1924,7 +1924,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1947,7 +1947,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1970,7 +1970,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1993,7 +1993,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -2016,7 +2016,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2039,7 +2039,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2062,7 +2062,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2085,7 +2085,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2108,7 +2108,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2131,7 +2131,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2154,7 +2154,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2177,7 +2177,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2200,7 +2200,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2223,7 +2223,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2246,7 +2246,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2269,7 +2269,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2292,7 +2292,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2315,7 +2315,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2338,7 +2338,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2361,7 +2361,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2384,7 +2384,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2407,7 +2407,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2430,7 +2430,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2453,7 +2453,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2476,7 +2476,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2499,7 +2499,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2522,7 +2522,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2545,7 +2545,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2568,7 +2568,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2591,7 +2591,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2614,7 +2614,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2637,7 +2637,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2660,7 +2660,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2683,7 +2683,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2706,7 +2706,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2729,7 +2729,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2752,7 +2752,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2775,7 +2775,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2798,7 +2798,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2821,7 +2821,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2844,7 +2844,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2867,7 +2867,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2890,7 +2890,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2913,7 +2913,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2936,7 +2936,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2959,7 +2959,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2982,7 +2982,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -3005,7 +3005,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3028,7 +3028,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3051,7 +3051,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3074,7 +3074,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3097,7 +3097,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3120,7 +3120,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3143,7 +3143,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3166,7 +3166,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3189,7 +3189,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>96</v>
       </c>
       <c r="F99" s="18">
-        <v>31249</v>
+        <v>29480</v>
       </c>
       <c r="G99" s="18">
         <v>781242</v>
@@ -3212,7 +3212,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>97</v>
       </c>
       <c r="F100" s="18">
-        <v>31249</v>
+        <v>29480</v>
       </c>
       <c r="G100" s="18">
         <v>781242</v>
@@ -3235,7 +3235,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>98</v>
       </c>
       <c r="F101" s="18">
-        <v>31249</v>
+        <v>29480</v>
       </c>
       <c r="G101" s="18">
         <v>781242</v>
@@ -3258,7 +3258,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>99</v>
       </c>
       <c r="F102" s="18">
-        <v>31249</v>
+        <v>29480</v>
       </c>
       <c r="G102" s="18">
         <v>781242</v>
@@ -3281,7 +3281,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>100</v>
       </c>
       <c r="F103" s="18">
-        <v>31249</v>
+        <v>29480</v>
       </c>
       <c r="G103" s="18">
         <v>781242</v>
@@ -3304,7 +3304,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>101</v>
       </c>
       <c r="F104" s="18">
-        <v>31249</v>
+        <v>29480</v>
       </c>
       <c r="G104" s="18">
         <v>781242</v>
@@ -3327,7 +3327,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>102</v>
       </c>
       <c r="F105" s="18">
-        <v>31249</v>
+        <v>29480</v>
       </c>
       <c r="G105" s="18">
         <v>781242</v>
@@ -3350,7 +3350,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>103</v>
       </c>
       <c r="F106" s="18">
-        <v>31249</v>
+        <v>29480</v>
       </c>
       <c r="G106" s="18">
         <v>781242</v>
@@ -3373,7 +3373,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>104</v>
       </c>
       <c r="F107" s="18">
-        <v>31249</v>
+        <v>29480</v>
       </c>
       <c r="G107" s="18">
         <v>781242</v>
@@ -3396,7 +3396,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>105</v>
       </c>
       <c r="F108" s="18">
-        <v>31249</v>
+        <v>29480</v>
       </c>
       <c r="G108" s="18">
         <v>781242</v>
@@ -3419,7 +3419,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="21" t="s">
         <v>8</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>106</v>
       </c>
       <c r="F109" s="24">
-        <v>20833</v>
+        <v>7861</v>
       </c>
       <c r="G109" s="24">
         <v>781242</v>
@@ -3442,7 +3442,7 @@
       <c r="I109" s="25"/>
       <c r="J109" s="26"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="32" t="s">
         <v>116</v>
       </c>
@@ -3453,7 +3453,7 @@
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="32" t="s">
         <v>115</v>
       </c>
